--- a/Test Execution Script.xlsx
+++ b/Test Execution Script.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORK\CASMEX_UI_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{584303CF-7820-45FF-BFFD-AED2925FA263}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85ED2AE7-766E-4A9C-9B81-76DB6564929E}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="98">
   <si>
     <t>AUTOMATION TEST SCRIPT</t>
   </si>
@@ -310,6 +310,18 @@
   </si>
   <si>
     <t>Search for customer code and verify if the customer name and last 5 transactions are displayed.</t>
+  </si>
+  <si>
+    <t>ABHIRAMAM</t>
+  </si>
+  <si>
+    <t>Test Data &amp; Expected Result</t>
+  </si>
+  <si>
+    <t>Search Type</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
   </si>
 </sst>
 </file>
@@ -355,7 +367,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -416,6 +428,30 @@
         <bgColor rgb="FF99CCFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor rgb="FF969696"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -429,7 +465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -508,6 +544,24 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -891,22 +945,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC483614-C058-4CEB-BC84-CD3DFD1E2D53}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.42578125" style="27" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="38.140625" style="27" customWidth="1" collapsed="1"/>
     <col min="3" max="3" width="39.7109375" style="27" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.85546875" style="27" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="12.140625" style="27" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="13" style="27" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="21.7109375" style="27" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="19.42578125" style="27" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="24.7109375" style="27" customWidth="1" collapsed="1"/>
     <col min="7" max="7" width="9.140625" style="27"/>
     <col min="8" max="8" width="14.7109375" style="27" customWidth="1" collapsed="1"/>
     <col min="9" max="9" width="25.140625" style="27" customWidth="1" collapsed="1"/>
     <col min="10" max="16384" width="9.140625" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="23"/>
       <c r="B1" s="23"/>
       <c r="C1" s="26" t="s">
@@ -914,7 +968,7 @@
       </c>
       <c r="D1" s="23"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
@@ -922,7 +976,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
         <v>3</v>
       </c>
@@ -930,7 +984,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
         <v>5</v>
       </c>
@@ -938,12 +992,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
         <v>8</v>
       </c>
@@ -954,7 +1008,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
         <v>9</v>
       </c>
@@ -965,7 +1019,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
         <v>11</v>
       </c>
@@ -973,7 +1027,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
         <v>13</v>
       </c>
@@ -981,7 +1035,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
         <v>15</v>
       </c>
@@ -989,7 +1043,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
         <v>17</v>
       </c>
@@ -997,7 +1051,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
         <v>19</v>
       </c>
@@ -1005,7 +1059,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
         <v>21</v>
       </c>
@@ -1013,7 +1067,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
         <v>23</v>
       </c>
@@ -1021,7 +1075,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="30" t="s">
         <v>92</v>
       </c>
@@ -1031,49 +1085,73 @@
       <c r="C16" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="D16" s="30" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
+      <c r="D16" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="36"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="32"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="F17" s="31" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B18" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C18" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="D17" s="25" t="s">
+      <c r="D18" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="E17" s="29" t="s">
+      <c r="E18" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="F17" s="29"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="25"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
+      <c r="F18" s="29" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="25"/>
+      <c r="B19" s="25"/>
       <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
       <c r="E19" s="25"/>
       <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="25"/>
       <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="25"/>
+      <c r="C21" s="25"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D16:I16"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/Test Execution Script.xlsx
+++ b/Test Execution Script.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORK\CASMEX_UI_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85ED2AE7-766E-4A9C-9B81-76DB6564929E}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A14805D-EAEB-4F83-BE74-16827E21207E}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="103">
   <si>
     <t>AUTOMATION TEST SCRIPT</t>
   </si>
@@ -294,9 +294,6 @@
     <t>Test Case Name</t>
   </si>
   <si>
-    <t>remittanceSearchTest</t>
-  </si>
-  <si>
     <t>Customer Code</t>
   </si>
   <si>
@@ -309,12 +306,6 @@
     <t>Test Name</t>
   </si>
   <si>
-    <t>Search for customer code and verify if the customer name and last 5 transactions are displayed.</t>
-  </si>
-  <si>
-    <t>ABHIRAMAM</t>
-  </si>
-  <si>
     <t>Test Data &amp; Expected Result</t>
   </si>
   <si>
@@ -322,6 +313,30 @@
   </si>
   <si>
     <t>Expected Result</t>
+  </si>
+  <si>
+    <t>00005091900001</t>
+  </si>
+  <si>
+    <t>BENFIRST BENMID BENLAST</t>
+  </si>
+  <si>
+    <t>TC001 - Search for customer code and verify if the latest transaction from the last 5 transactions is valid.</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>96855412548</t>
+  </si>
+  <si>
+    <t>TC002 - Search for mobile and verify if the beneficiary name tagged to this mobile number appears correctly.</t>
+  </si>
+  <si>
+    <t>searchCustomerCode</t>
+  </si>
+  <si>
+    <t>searchMobile</t>
   </si>
 </sst>
 </file>
@@ -945,7 +960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC483614-C058-4CEB-BC84-CD3DFD1E2D53}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.42578125" style="27" customWidth="1" collapsed="1"/>
@@ -953,7 +968,7 @@
     <col min="3" max="3" width="39.7109375" style="27" customWidth="1" collapsed="1"/>
     <col min="4" max="4" width="21.7109375" style="27" customWidth="1" collapsed="1"/>
     <col min="5" max="5" width="19.42578125" style="27" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="24.7109375" style="27" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="27.5703125" style="27" customWidth="1" collapsed="1"/>
     <col min="7" max="7" width="9.140625" style="27"/>
     <col min="8" max="8" width="14.7109375" style="27" customWidth="1" collapsed="1"/>
     <col min="9" max="9" width="25.140625" style="27" customWidth="1" collapsed="1"/>
@@ -1077,16 +1092,16 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B16" s="30" t="s">
         <v>87</v>
       </c>
       <c r="C16" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E16" s="36"/>
       <c r="F16" s="36"/>
@@ -1094,59 +1109,73 @@
       <c r="H16" s="36"/>
       <c r="I16" s="36"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="32"/>
       <c r="B17" s="33"/>
       <c r="C17" s="32"/>
       <c r="D17" s="34" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="s">
         <v>86</v>
       </c>
       <c r="B18" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="E18" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" s="29" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="32"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="E18" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="F18" s="29" t="s">
+      <c r="E19" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="F19" s="31" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="25"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="25"/>
-      <c r="C21" s="25"/>
+    <row r="20" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="F20" s="27" t="s">
+        <v>96</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
